--- a/data/config/luban/config/general/name.xlsx
+++ b/data/config/luban/config/general/name.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$E$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,24 +30,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>item_template_id</t>
+    <t>id</t>
   </si>
   <si>
-    <t>#name</t>
+    <t>name</t>
   </si>
   <si>
-    <t>item_type</t>
+    <t>sex_type</t>
   </si>
   <si>
-    <t>stacked</t>
-  </si>
-  <si>
-    <t>squares</t>
+    <t>weight</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,22 +53,22 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
+    <t>string</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>物品编号</t>
+    <t>名字</t>
   </si>
   <si>
-    <t>物品名称</t>
+    <t>性别</t>
   </si>
   <si>
-    <t>物品类型</t>
+    <t>权重</t>
   </si>
   <si>
-    <t>金币</t>
+    <t>给</t>
   </si>
 </sst>
 </file>
@@ -1259,18 +1256,17 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
-    <col min="4" max="5" width="26" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="29.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1286,70 +1282,67 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:5">
+      <c r="B4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:6">
-      <c r="B4" s="2">
-        <v>10001</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:E4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  <conditionalFormatting sqref="B5:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
